--- a/onluyen_data/69cc7f41b86b57e0fac47636.xlsx
+++ b/onluyen_data/69cc7f41b86b57e0fac47636.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dap an" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Thong ke" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dap an" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thong ke" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,6 +40,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
@@ -47,11 +52,6 @@
       <b val="1"/>
       <color rgb="00C0392B"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -96,7 +96,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -118,11 +118,44 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -130,37 +163,39 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -575,299 +610,250 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Dung sai</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>ĐSSĐ</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ĐĐSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>SSSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>SSSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Dien</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>0,11.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Trac nghiem</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Dung sai</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>ĐĐSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Dien</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>0,61</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Trac nghiem</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Dung sai</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>SSSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Dien</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Trac nghiem</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Dung sai</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>SSSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Dien</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Trac nghiem</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Dien</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Trac nghiem</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Dien</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>1595</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Trac nghiem</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A19:A24"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A3:A14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -888,63 +874,63 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Dang cau</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>So luong</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Tong diem</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Trac nghiem</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
+      <c r="B2" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="15" t="n">
         <v>5.454</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Dung sai</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="16" t="n">
         <v>1.818</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Dien</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="17" t="n">
         <v>2.728</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>TONG</t>
         </is>

--- a/onluyen_data/69cc7f41b86b57e0fac47636.xlsx
+++ b/onluyen_data/69cc7f41b86b57e0fac47636.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dap an" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thong ke" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dap an" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Thong ke" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
